--- a/bakup/customers/danial.xlsx
+++ b/bakup/customers/danial.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -282,7 +282,16 @@
     <t>گول بازی مزه باغ دامو</t>
   </si>
   <si>
-    <t>1405/05/23</t>
+    <t>1405/05/26</t>
+  </si>
+  <si>
+    <t>1405/06/01</t>
+  </si>
+  <si>
+    <t>مزه</t>
+  </si>
+  <si>
+    <t>1405/06/02</t>
   </si>
 </sst>
 </file>
@@ -723,6 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -759,7 +769,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1934,27 +1944,39 @@
     <row r="81" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
-      </c>
-      <c r="B81" s="6"/>
+        <v>2386000</v>
+      </c>
+      <c r="B81" s="6">
+        <v>71000</v>
+      </c>
       <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-      <c r="E81" s="3"/>
+      <c r="D81" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="82" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
-      </c>
-      <c r="B82" s="6"/>
+        <v>2575000</v>
+      </c>
+      <c r="B82" s="6">
+        <v>189000</v>
+      </c>
       <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="3"/>
+      <c r="D82" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="83" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -1964,7 +1986,7 @@
     <row r="84" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -1974,7 +1996,7 @@
     <row r="85" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1984,7 +2006,7 @@
     <row r="86" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -1994,7 +2016,7 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2004,7 +2026,7 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2014,7 +2036,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2024,7 +2046,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2034,7 +2056,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2044,7 +2066,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2054,7 +2076,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2064,7 +2086,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2074,7 +2096,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2085,7 +2107,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>6233000</v>
+        <v>6493000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2097,7 +2119,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2315000</v>
+        <v>2575000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">
